--- a/public/templates/000_pm_suite/02_프로젝트 개발/02_착수/05_Workshop/프로젝트명_워크샵계획서_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/02_프로젝트 개발/02_착수/05_Workshop/프로젝트명_워크샵계획서_V1.0_20230530.xlsx
@@ -518,14 +518,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-32] 한빛글로벌 SyncGuard AI 착수 및 요구분석 합동 워크샵 계획서 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-32] 한빛글로벌 SyncFlow AI 착수 및 요구분석 합동 워크샵 계획서 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>발주처(규제심의팀·마케팅팀·IT정보화팀) 및 수행사 합동 도메인 정책·연계 규격 확정 워크샵 아젠다 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+          <t>발주처(규제검증팀·구매조달팀·IT정보화팀) 및 수행사 합동 도메인 정책·연계 규격 확정 워크샵 아젠다 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
         </is>
       </c>
     </row>
@@ -616,12 +616,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>AS-IS 심의 병목 및 61대 요구사항 리뷰</t>
+          <t>AS-IS 검증 병목 및 61대 요구사항 리뷰</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>현행 브랜드별 표시·광고 심의 프로세스 점검 및 61개 요구사항 우선순위 확정</t>
+          <t>현행 사업부별 계약·기술규격 검증 프로세스 점검 및 61개 요구사항 우선순위 확정</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>윤서연 팀장 외 규제심의팀</t>
+          <t>윤서연 팀장 외 규제검증팀</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>의약품 오인·절대적 표현·전성분 배합한도 룰셋 기준 및 평가용 골든셋 확정</t>
+          <t>불공정 독소조항·절대적 표현·자재BOM 유해물질한도 룰셋 기준 및 평가용 골든셋 확정</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>규제심의팀 / 법률자문역</t>
+          <t>규제검증팀 / 법률자문역</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>멀티모달 업로드, OCR 영역 보정, 신호등 결과 리포트 및 대체문구 추천 화면 시연</t>
+          <t>멀티모달 업로드, OCR 영역 보정, 신호등 결과 리포트 및 표준수정조항 추천 화면 시연</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>마케팅팀 / 규제심의팀</t>
+          <t>구매조달팀 / 규제검증팀</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>HB-SSO, ProductLab 02:00 일배치, MarketingHub Webhook 및 방화벽 오픈 일정 합의</t>
+          <t>HB-SSO, PLM-Nexus 02:00 일배치, SRM-Portal Webhook 및 방화벽 오픈 일정 합의</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
